--- a/Caja/REPORTE CAJAS EFECTIVO DOLAR 2025.xlsx
+++ b/Caja/REPORTE CAJAS EFECTIVO DOLAR 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\italm\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasb/Escritorio - MacBook Air de Lucas/Fornitalia/Caja/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A161C733-7EB3-406A-BF5A-0B0E65DFE07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1D8171-717A-2348-B793-1CE88F1E5366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E10EBC3-F181-3D49-BEE0-454AD2394888}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="23260" windowHeight="12460" activeTab="6" xr2:uid="{6E10EBC3-F181-3D49-BEE0-454AD2394888}"/>
   </bookViews>
   <sheets>
     <sheet name="Mayo" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Octubre!$A$1:$Y$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Septiembre!$A$1:$Y$5</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -776,34 +776,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC2B3CBE-DAB2-4B44-8001-6DAFEB94D4EF}">
   <dimension ref="A1:Y4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.69921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="12.5" customWidth="1"/>
-    <col min="9" max="9" width="18.8984375" customWidth="1"/>
-    <col min="10" max="10" width="65.59765625" customWidth="1"/>
-    <col min="11" max="11" width="17.09765625" customWidth="1"/>
-    <col min="12" max="12" width="29.69921875" customWidth="1"/>
-    <col min="13" max="13" width="19.296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="65.6640625" customWidth="1"/>
+    <col min="11" max="11" width="17.1640625" customWidth="1"/>
+    <col min="12" max="12" width="29.6640625" customWidth="1"/>
+    <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="7.296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="42.296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="42.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -880,7 +880,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -936,7 +936,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -986,7 +986,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -1045,34 +1045,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC8F396F-8401-46F0-9117-7551811118E8}">
   <dimension ref="A1:Y3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.69921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="12.5" customWidth="1"/>
-    <col min="9" max="9" width="18.8984375" customWidth="1"/>
-    <col min="10" max="10" width="65.59765625" customWidth="1"/>
-    <col min="11" max="11" width="17.09765625" customWidth="1"/>
-    <col min="12" max="12" width="29.69921875" customWidth="1"/>
-    <col min="13" max="13" width="19.296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="65.6640625" customWidth="1"/>
+    <col min="11" max="11" width="17.1640625" customWidth="1"/>
+    <col min="12" max="12" width="29.6640625" customWidth="1"/>
+    <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="7.296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="42.296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="42.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -1264,34 +1264,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42D44CA8-3A30-42F8-B9ED-EB77EAFF007B}">
   <dimension ref="A1:Y6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.69921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="12.5" customWidth="1"/>
-    <col min="9" max="9" width="18.8984375" customWidth="1"/>
-    <col min="10" max="10" width="65.59765625" customWidth="1"/>
-    <col min="11" max="11" width="17.09765625" customWidth="1"/>
-    <col min="12" max="12" width="29.69921875" customWidth="1"/>
-    <col min="13" max="13" width="19.296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="65.6640625" customWidth="1"/>
+    <col min="11" max="11" width="17.1640625" customWidth="1"/>
+    <col min="12" max="12" width="29.6640625" customWidth="1"/>
+    <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="7.296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="42.296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="42.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -1663,34 +1663,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EA45231-CE6A-4A2C-B4A2-661C235CAADF}">
   <dimension ref="A1:Y3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.69921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="12.5" customWidth="1"/>
-    <col min="9" max="9" width="18.8984375" customWidth="1"/>
-    <col min="10" max="10" width="65.59765625" customWidth="1"/>
-    <col min="11" max="11" width="17.09765625" customWidth="1"/>
-    <col min="12" max="12" width="29.69921875" customWidth="1"/>
-    <col min="13" max="13" width="19.296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="65.6640625" customWidth="1"/>
+    <col min="11" max="11" width="17.1640625" customWidth="1"/>
+    <col min="12" max="12" width="29.6640625" customWidth="1"/>
+    <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="7.296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="42.296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="42.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -1906,34 +1906,34 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E3E79F-1B86-4BB3-8CBC-54CEE37C92BD}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.69921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="12.5" customWidth="1"/>
-    <col min="9" max="9" width="18.8984375" customWidth="1"/>
-    <col min="10" max="10" width="65.59765625" customWidth="1"/>
-    <col min="11" max="11" width="17.09765625" customWidth="1"/>
-    <col min="12" max="12" width="29.69921875" customWidth="1"/>
-    <col min="13" max="13" width="19.296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="65.6640625" customWidth="1"/>
+    <col min="11" max="11" width="17.1640625" customWidth="1"/>
+    <col min="12" max="12" width="29.6640625" customWidth="1"/>
+    <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="7.296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="42.296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="42.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -2249,34 +2249,34 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{720823A4-DCA5-49F1-9768-515C800C035A}">
   <dimension ref="A1:Y6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.69921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="12.5" customWidth="1"/>
-    <col min="9" max="9" width="18.8984375" customWidth="1"/>
-    <col min="10" max="10" width="65.59765625" customWidth="1"/>
-    <col min="11" max="11" width="17.09765625" customWidth="1"/>
-    <col min="12" max="12" width="29.69921875" customWidth="1"/>
-    <col min="13" max="13" width="19.296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="65.6640625" customWidth="1"/>
+    <col min="11" max="11" width="17.1640625" customWidth="1"/>
+    <col min="12" max="12" width="29.6640625" customWidth="1"/>
+    <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="7.296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="42.296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="42.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -2663,34 +2663,34 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3987C73D-B1CB-40F1-A1A5-0040221FBB47}">
   <dimension ref="A1:Y6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.69921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="12.5" customWidth="1"/>
-    <col min="9" max="9" width="18.8984375" customWidth="1"/>
-    <col min="10" max="10" width="65.59765625" customWidth="1"/>
-    <col min="11" max="11" width="17.09765625" customWidth="1"/>
-    <col min="12" max="12" width="29.69921875" customWidth="1"/>
-    <col min="13" max="13" width="19.296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="65.6640625" customWidth="1"/>
+    <col min="11" max="11" width="17.1640625" customWidth="1"/>
+    <col min="12" max="12" width="29.6640625" customWidth="1"/>
+    <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="7.296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="42.296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="42.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -3053,34 +3053,34 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04E2F44C-2CAD-43B2-B8F0-3E70527CA8ED}">
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.69921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="12.5" customWidth="1"/>
-    <col min="9" max="9" width="18.8984375" customWidth="1"/>
-    <col min="10" max="10" width="65.59765625" customWidth="1"/>
-    <col min="11" max="11" width="17.09765625" customWidth="1"/>
-    <col min="12" max="12" width="29.69921875" customWidth="1"/>
-    <col min="13" max="13" width="19.296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="65.6640625" customWidth="1"/>
+    <col min="11" max="11" width="17.1640625" customWidth="1"/>
+    <col min="12" max="12" width="29.6640625" customWidth="1"/>
+    <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="7.296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="42.296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="42.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -3346,7 +3346,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -3603,7 +3603,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -3733,7 +3733,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>25</v>
       </c>
